--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="241" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{237114F3-0B05-4264-A9B0-0EB88D6699E9}"/>
+  <xr:revisionPtr revIDLastSave="258" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9894EFB0-A988-4336-B26B-7FA4089B0409}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
+    <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -44,10 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
-  <si>
-    <t>Puntoff Leaderboard</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
   <si>
     <t>Phil</t>
   </si>
@@ -91,9 +88,6 @@
     <t>% Return</t>
   </si>
   <si>
-    <t>Punters</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bets up to Round </t>
   </si>
   <si>
@@ -104,6 +98,9 @@
   </si>
   <si>
     <t>Total Bet</t>
+  </si>
+  <si>
+    <t>Punter</t>
   </si>
 </sst>
 </file>
@@ -586,99 +583,99 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B1" s="7"/>
     </row>
     <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="13">
         <f>+Rounds!B6*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C4" s="13">
         <f>SUM(Rounds!C6:BB6)</f>
-        <v>195.74</v>
+        <v>199.74</v>
       </c>
       <c r="D4" s="8">
         <f>+C4/(Rounds!$B$3*Rounds!B6)</f>
-        <v>1.6311666666666667</v>
+        <v>1.4267142857142858</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="13">
         <f>+Rounds!B7*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C5" s="13">
         <f>SUM(Rounds!C7:BB7)</f>
-        <v>190</v>
+        <v>757</v>
       </c>
       <c r="D5" s="8">
         <f>+C5/(Rounds!$B$3*Rounds!B7)</f>
-        <v>1.5833333333333333</v>
+        <v>5.4071428571428575</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="13">
         <f>+Rounds!B8*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C6" s="13">
         <f>SUM(Rounds!C8:BB8)</f>
-        <v>180.37</v>
+        <v>214.37</v>
       </c>
       <c r="D6" s="8">
         <f>+C6/(Rounds!$B$3*Rounds!B8)</f>
-        <v>1.5030833333333333</v>
+        <v>1.5312142857142856</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B7" s="13">
         <f>+Rounds!B9*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C7" s="13">
         <f>SUM(Rounds!C9:BB9)</f>
-        <v>157.35</v>
+        <v>513.35</v>
       </c>
       <c r="D7" s="8">
         <f>+C7/(Rounds!$B$3*Rounds!B9)</f>
-        <v>1.31125</v>
+        <v>3.6667857142857145</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" s="13">
         <f>+Rounds!B10*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C8" s="13">
         <f>SUM(Rounds!C10:BB10)</f>
@@ -686,16 +683,16 @@
       </c>
       <c r="D8" s="8">
         <f>+C8/(Rounds!$B$3*Rounds!B10)</f>
-        <v>1.2166666666666666</v>
+        <v>1.0428571428571429</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="13">
         <f>+Rounds!B11*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C9" s="13">
         <f>SUM(Rounds!C11:BB11)</f>
@@ -703,16 +700,16 @@
       </c>
       <c r="D9" s="8">
         <f>+C9/(Rounds!$B$3*Rounds!B11)</f>
-        <v>1.1583333333333334</v>
+        <v>0.99285714285714288</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" s="13">
         <f>+Rounds!B12*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C10" s="13">
         <f>SUM(Rounds!C12:BB12)</f>
@@ -720,58 +717,58 @@
       </c>
       <c r="D10" s="8">
         <f>+C10/(Rounds!$B$3*Rounds!B12)</f>
-        <v>0.74324999999999997</v>
+        <v>0.63707142857142851</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="13">
         <f>+Rounds!B13*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C11" s="13">
         <f>SUM(Rounds!C13:BB13)</f>
-        <v>84</v>
+        <v>972</v>
       </c>
       <c r="D11" s="8">
         <f>+C11/(Rounds!$B$3*Rounds!B13)</f>
-        <v>0.7</v>
+        <v>6.9428571428571431</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="13">
         <f>+Rounds!B14*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C12" s="13">
         <f>SUM(Rounds!C14:BB14)</f>
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="D12" s="8">
         <f>+C12/(Rounds!$B$3*Rounds!B14)</f>
-        <v>0.58333333333333337</v>
+        <v>0.58571428571428574</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="13">
         <f>+Rounds!B15*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C13" s="13">
         <f>SUM(Rounds!C15:BB15)</f>
-        <v>30.939999999999998</v>
+        <v>33.94</v>
       </c>
       <c r="D13" s="8">
         <f>+C13/(Rounds!$B$3*Rounds!B15)</f>
-        <v>0.2578333333333333</v>
+        <v>0.24242857142857141</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -782,19 +779,19 @@
     </row>
     <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="15">
         <f>SUM(B4:B13)</f>
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="C15" s="14">
         <f>SUM(C4:C13)</f>
-        <v>1282.5900000000001</v>
+        <v>3146.59</v>
       </c>
       <c r="D15" s="10">
         <f>+C15/(Rounds!$B$3*Rounds!B16)</f>
-        <v>1.0688250000000001</v>
+        <v>2.2475642857142857</v>
       </c>
     </row>
   </sheetData>
@@ -819,15 +816,15 @@
   <sheetData>
     <row r="1" spans="1:54" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B3" s="12">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.2">
@@ -835,10 +832,10 @@
     </row>
     <row r="5" spans="1:54" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="4">
         <v>1</v>
@@ -1050,7 +1047,7 @@
     </row>
     <row r="6" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="17">
         <v>20</v>
@@ -1067,7 +1064,9 @@
       <c r="H6" s="17">
         <v>64</v>
       </c>
-      <c r="I6" s="17"/>
+      <c r="I6" s="17">
+        <v>4</v>
+      </c>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
@@ -1116,7 +1115,7 @@
     </row>
     <row r="7" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="17">
         <f>+B6</f>
@@ -1132,7 +1131,9 @@
       <c r="H7" s="17">
         <v>150</v>
       </c>
-      <c r="I7" s="17"/>
+      <c r="I7" s="17">
+        <v>567</v>
+      </c>
       <c r="J7" s="17"/>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
@@ -1181,7 +1182,7 @@
     </row>
     <row r="8" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="17">
         <f t="shared" ref="B8:B15" si="3">+B7</f>
@@ -1199,7 +1200,9 @@
       <c r="H8" s="17">
         <v>65.67</v>
       </c>
-      <c r="I8" s="17"/>
+      <c r="I8" s="17">
+        <v>34</v>
+      </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
@@ -1248,7 +1251,7 @@
     </row>
     <row r="9" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9" s="17">
         <f t="shared" si="3"/>
@@ -1264,7 +1267,9 @@
       </c>
       <c r="G9" s="17"/>
       <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
+      <c r="I9" s="17">
+        <v>356</v>
+      </c>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
@@ -1313,7 +1318,7 @@
     </row>
     <row r="10" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" s="17">
         <f t="shared" si="3"/>
@@ -1378,7 +1383,7 @@
     </row>
     <row r="11" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="17">
         <f t="shared" si="3"/>
@@ -1445,7 +1450,7 @@
     </row>
     <row r="12" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="17">
         <f t="shared" si="3"/>
@@ -1512,7 +1517,7 @@
     </row>
     <row r="13" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" s="17">
         <f t="shared" si="3"/>
@@ -1528,7 +1533,9 @@
       <c r="H13" s="17">
         <v>50</v>
       </c>
-      <c r="I13" s="17"/>
+      <c r="I13" s="17">
+        <v>888</v>
+      </c>
       <c r="J13" s="17"/>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
@@ -1577,7 +1584,7 @@
     </row>
     <row r="14" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="17">
         <f t="shared" si="3"/>
@@ -1591,7 +1598,9 @@
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
+      <c r="I14" s="17">
+        <v>12</v>
+      </c>
       <c r="J14" s="17"/>
       <c r="K14" s="17"/>
       <c r="L14" s="17"/>
@@ -1640,7 +1649,7 @@
     </row>
     <row r="15" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" s="17">
         <f t="shared" si="3"/>
@@ -1656,7 +1665,9 @@
       <c r="H15" s="17">
         <v>18.5</v>
       </c>
-      <c r="I15" s="17"/>
+      <c r="I15" s="17">
+        <v>3</v>
+      </c>
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
@@ -1705,7 +1716,7 @@
     </row>
     <row r="16" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" s="18">
         <f>SUM(B6:B15)</f>
@@ -1737,7 +1748,7 @@
       </c>
       <c r="I16" s="18">
         <f t="shared" ref="I16" si="5">SUM(I6:I15)</f>
-        <v>0</v>
+        <v>1864</v>
       </c>
       <c r="J16" s="18">
         <f t="shared" ref="J16" si="6">SUM(J6:J15)</f>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="260" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84E530D3-EAB7-44AC-BF57-D58CC43AD875}"/>
+  <xr:revisionPtr revIDLastSave="264" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08567FA1-D48F-4C6D-B426-D8B1F82A8C4A}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
@@ -607,15 +607,15 @@
       </c>
       <c r="B4" s="13">
         <f>+Rounds!B6*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C4" s="13">
         <f>SUM(Rounds!C6:BB6)</f>
-        <v>199.74</v>
+        <v>195.74</v>
       </c>
       <c r="D4" s="8">
         <f>+C4/(Rounds!$B$3*Rounds!B6)</f>
-        <v>1.4267142857142858</v>
+        <v>1.6311666666666667</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -624,15 +624,15 @@
       </c>
       <c r="B5" s="13">
         <f>+Rounds!B7*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C5" s="13">
         <f>SUM(Rounds!C7:BB7)</f>
-        <v>757</v>
+        <v>190</v>
       </c>
       <c r="D5" s="8">
         <f>+C5/(Rounds!$B$3*Rounds!B7)</f>
-        <v>5.4071428571428575</v>
+        <v>1.5833333333333333</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -641,15 +641,15 @@
       </c>
       <c r="B6" s="13">
         <f>+Rounds!B8*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C6" s="13">
         <f>SUM(Rounds!C8:BB8)</f>
-        <v>214.37</v>
+        <v>180.37</v>
       </c>
       <c r="D6" s="8">
         <f>+C6/(Rounds!$B$3*Rounds!B8)</f>
-        <v>1.5312142857142856</v>
+        <v>1.5030833333333333</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -658,15 +658,15 @@
       </c>
       <c r="B7" s="13">
         <f>+Rounds!B9*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C7" s="13">
         <f>SUM(Rounds!C9:BB9)</f>
-        <v>513.35</v>
+        <v>157.35</v>
       </c>
       <c r="D7" s="8">
         <f>+C7/(Rounds!$B$3*Rounds!B9)</f>
-        <v>3.6667857142857145</v>
+        <v>1.31125</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -675,7 +675,7 @@
       </c>
       <c r="B8" s="13">
         <f>+Rounds!B10*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C8" s="13">
         <f>SUM(Rounds!C10:BB10)</f>
@@ -683,7 +683,7 @@
       </c>
       <c r="D8" s="8">
         <f>+C8/(Rounds!$B$3*Rounds!B10)</f>
-        <v>1.0428571428571429</v>
+        <v>1.2166666666666666</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -692,7 +692,7 @@
       </c>
       <c r="B9" s="13">
         <f>+Rounds!B11*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C9" s="13">
         <f>SUM(Rounds!C11:BB11)</f>
@@ -700,7 +700,7 @@
       </c>
       <c r="D9" s="8">
         <f>+C9/(Rounds!$B$3*Rounds!B11)</f>
-        <v>0.99285714285714288</v>
+        <v>1.1583333333333334</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -709,7 +709,7 @@
       </c>
       <c r="B10" s="13">
         <f>+Rounds!B12*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C10" s="13">
         <f>SUM(Rounds!C12:BB12)</f>
@@ -717,7 +717,7 @@
       </c>
       <c r="D10" s="8">
         <f>+C10/(Rounds!$B$3*Rounds!B12)</f>
-        <v>0.63707142857142851</v>
+        <v>0.74324999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -726,15 +726,15 @@
       </c>
       <c r="B11" s="13">
         <f>+Rounds!B13*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C11" s="13">
         <f>SUM(Rounds!C13:BB13)</f>
-        <v>972</v>
+        <v>84</v>
       </c>
       <c r="D11" s="8">
         <f>+C11/(Rounds!$B$3*Rounds!B13)</f>
-        <v>6.9428571428571431</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -743,15 +743,15 @@
       </c>
       <c r="B12" s="13">
         <f>+Rounds!B14*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C12" s="13">
         <f>SUM(Rounds!C14:BB14)</f>
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D12" s="8">
         <f>+C12/(Rounds!$B$3*Rounds!B14)</f>
-        <v>0.58571428571428574</v>
+        <v>0.58333333333333337</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -760,15 +760,15 @@
       </c>
       <c r="B13" s="13">
         <f>+Rounds!B15*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C13" s="13">
         <f>SUM(Rounds!C15:BB15)</f>
-        <v>33.94</v>
+        <v>30.939999999999998</v>
       </c>
       <c r="D13" s="8">
         <f>+C13/(Rounds!$B$3*Rounds!B15)</f>
-        <v>0.24242857142857141</v>
+        <v>0.2578333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -783,15 +783,15 @@
       </c>
       <c r="B15" s="15">
         <f>SUM(B4:B13)</f>
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="C15" s="14">
         <f>SUM(C4:C13)</f>
-        <v>3146.59</v>
+        <v>1282.5900000000001</v>
       </c>
       <c r="D15" s="10">
         <f>+C15/(Rounds!$B$3*Rounds!B16)</f>
-        <v>2.2475642857142857</v>
+        <v>1.0688250000000001</v>
       </c>
     </row>
   </sheetData>
@@ -824,7 +824,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.2">
@@ -1064,9 +1064,7 @@
       <c r="H6" s="17">
         <v>64</v>
       </c>
-      <c r="I6" s="17">
-        <v>4</v>
-      </c>
+      <c r="I6" s="17"/>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
@@ -1131,9 +1129,7 @@
       <c r="H7" s="17">
         <v>150</v>
       </c>
-      <c r="I7" s="17">
-        <v>567</v>
-      </c>
+      <c r="I7" s="17"/>
       <c r="J7" s="17"/>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
@@ -1200,9 +1196,7 @@
       <c r="H8" s="17">
         <v>65.67</v>
       </c>
-      <c r="I8" s="17">
-        <v>34</v>
-      </c>
+      <c r="I8" s="17"/>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
@@ -1267,9 +1261,7 @@
       </c>
       <c r="G9" s="17"/>
       <c r="H9" s="17"/>
-      <c r="I9" s="17">
-        <v>356</v>
-      </c>
+      <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
@@ -1533,9 +1525,7 @@
       <c r="H13" s="17">
         <v>50</v>
       </c>
-      <c r="I13" s="17">
-        <v>888</v>
-      </c>
+      <c r="I13" s="17"/>
       <c r="J13" s="17"/>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
@@ -1598,9 +1588,7 @@
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
-      <c r="I14" s="17">
-        <v>12</v>
-      </c>
+      <c r="I14" s="17"/>
       <c r="J14" s="17"/>
       <c r="K14" s="17"/>
       <c r="L14" s="17"/>
@@ -1665,9 +1653,7 @@
       <c r="H15" s="17">
         <v>18.5</v>
       </c>
-      <c r="I15" s="17">
-        <v>3</v>
-      </c>
+      <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
@@ -1748,7 +1734,7 @@
       </c>
       <c r="I16" s="18">
         <f t="shared" ref="I16" si="5">SUM(I6:I15)</f>
-        <v>1864</v>
+        <v>0</v>
       </c>
       <c r="J16" s="18">
         <f t="shared" ref="J16" si="6">SUM(J6:J15)</f>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="269" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8F3A2B6-A3A5-42D2-8ED1-EC01A4727E72}"/>
+  <xr:revisionPtr revIDLastSave="271" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA5FB1BD-2A25-4461-8BAD-4CC1B77B78B8}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
@@ -255,6 +255,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -607,15 +611,15 @@
       </c>
       <c r="B4" s="13">
         <f>+Rounds!B6*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C4" s="13">
         <f>SUM(Rounds!C6:BB6)</f>
-        <v>329.74</v>
+        <v>195.74</v>
       </c>
       <c r="D4" s="8">
         <f>+C4/(Rounds!$B$3*Rounds!B6)</f>
-        <v>2.3552857142857144</v>
+        <v>1.6311666666666667</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -624,7 +628,7 @@
       </c>
       <c r="B5" s="13">
         <f>+Rounds!B7*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C5" s="13">
         <f>SUM(Rounds!C7:BB7)</f>
@@ -632,7 +636,7 @@
       </c>
       <c r="D5" s="8">
         <f>+C5/(Rounds!$B$3*Rounds!B7)</f>
-        <v>1.3571428571428572</v>
+        <v>1.5833333333333333</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -641,7 +645,7 @@
       </c>
       <c r="B6" s="13">
         <f>+Rounds!B8*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C6" s="13">
         <f>SUM(Rounds!C8:BB8)</f>
@@ -649,7 +653,7 @@
       </c>
       <c r="D6" s="8">
         <f>+C6/(Rounds!$B$3*Rounds!B8)</f>
-        <v>1.288357142857143</v>
+        <v>1.5030833333333333</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -658,15 +662,15 @@
       </c>
       <c r="B7" s="13">
         <f>+Rounds!B9*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C7" s="13">
         <f>SUM(Rounds!C9:BB9)</f>
-        <v>502.35</v>
+        <v>157.35</v>
       </c>
       <c r="D7" s="8">
         <f>+C7/(Rounds!$B$3*Rounds!B9)</f>
-        <v>3.5882142857142858</v>
+        <v>1.31125</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -675,7 +679,7 @@
       </c>
       <c r="B8" s="13">
         <f>+Rounds!B10*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C8" s="13">
         <f>SUM(Rounds!C10:BB10)</f>
@@ -683,7 +687,7 @@
       </c>
       <c r="D8" s="8">
         <f>+C8/(Rounds!$B$3*Rounds!B10)</f>
-        <v>1.0428571428571429</v>
+        <v>1.2166666666666666</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -692,7 +696,7 @@
       </c>
       <c r="B9" s="13">
         <f>+Rounds!B11*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C9" s="13">
         <f>SUM(Rounds!C11:BB11)</f>
@@ -700,7 +704,7 @@
       </c>
       <c r="D9" s="8">
         <f>+C9/(Rounds!$B$3*Rounds!B11)</f>
-        <v>0.99285714285714288</v>
+        <v>1.1583333333333334</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -709,15 +713,15 @@
       </c>
       <c r="B10" s="13">
         <f>+Rounds!B12*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C10" s="13">
         <f>SUM(Rounds!C12:BB12)</f>
-        <v>434.19</v>
+        <v>89.19</v>
       </c>
       <c r="D10" s="8">
         <f>+C10/(Rounds!$B$3*Rounds!B12)</f>
-        <v>3.1013571428571427</v>
+        <v>0.74324999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -726,7 +730,7 @@
       </c>
       <c r="B11" s="13">
         <f>+Rounds!B13*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C11" s="13">
         <f>SUM(Rounds!C13:BB13)</f>
@@ -734,7 +738,7 @@
       </c>
       <c r="D11" s="8">
         <f>+C11/(Rounds!$B$3*Rounds!B13)</f>
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -743,7 +747,7 @@
       </c>
       <c r="B12" s="13">
         <f>+Rounds!B14*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C12" s="13">
         <f>SUM(Rounds!C14:BB14)</f>
@@ -751,7 +755,7 @@
       </c>
       <c r="D12" s="8">
         <f>+C12/(Rounds!$B$3*Rounds!B14)</f>
-        <v>0.5</v>
+        <v>0.58333333333333337</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -760,15 +764,15 @@
       </c>
       <c r="B13" s="13">
         <f>+Rounds!B15*Rounds!$B$3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C13" s="13">
         <f>SUM(Rounds!C15:BB15)</f>
-        <v>42.94</v>
+        <v>30.939999999999998</v>
       </c>
       <c r="D13" s="8">
         <f>+C13/(Rounds!$B$3*Rounds!B15)</f>
-        <v>0.30671428571428572</v>
+        <v>0.2578333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -783,15 +787,15 @@
       </c>
       <c r="B15" s="15">
         <f>SUM(B4:B13)</f>
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="C15" s="14">
         <f>SUM(C4:C13)</f>
-        <v>2118.59</v>
+        <v>1282.5900000000001</v>
       </c>
       <c r="D15" s="10">
         <f>+C15/(Rounds!$B$3*Rounds!B16)</f>
-        <v>1.5132785714285715</v>
+        <v>1.0688250000000001</v>
       </c>
     </row>
   </sheetData>
@@ -824,7 +828,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.2">
@@ -1064,9 +1068,7 @@
       <c r="H6" s="17">
         <v>64</v>
       </c>
-      <c r="I6" s="17">
-        <v>134</v>
-      </c>
+      <c r="I6" s="17"/>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
@@ -1263,9 +1265,7 @@
       </c>
       <c r="G9" s="17"/>
       <c r="H9" s="17"/>
-      <c r="I9" s="17">
-        <v>345</v>
-      </c>
+      <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
@@ -1464,9 +1464,7 @@
         <v>20</v>
       </c>
       <c r="H12" s="17"/>
-      <c r="I12" s="17">
-        <v>345</v>
-      </c>
+      <c r="I12" s="17"/>
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
@@ -1659,9 +1657,7 @@
       <c r="H15" s="17">
         <v>18.5</v>
       </c>
-      <c r="I15" s="17">
-        <v>12</v>
-      </c>
+      <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
@@ -1742,7 +1738,7 @@
       </c>
       <c r="I16" s="18">
         <f t="shared" ref="I16" si="5">SUM(I6:I15)</f>
-        <v>836</v>
+        <v>0</v>
       </c>
       <c r="J16" s="18">
         <f t="shared" ref="J16" si="6">SUM(J6:J15)</f>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="271" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA5FB1BD-2A25-4461-8BAD-4CC1B77B78B8}"/>
+  <xr:revisionPtr revIDLastSave="277" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FEE87DA-A963-4BC0-B949-C978FB7A1DA4}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
@@ -611,15 +611,15 @@
       </c>
       <c r="B4" s="13">
         <f>+Rounds!B6*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C4" s="13">
         <f>SUM(Rounds!C6:BB6)</f>
-        <v>195.74</v>
+        <v>271.74</v>
       </c>
       <c r="D4" s="8">
         <f>+C4/(Rounds!$B$3*Rounds!B6)</f>
-        <v>1.6311666666666667</v>
+        <v>1.9410000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -628,7 +628,7 @@
       </c>
       <c r="B5" s="13">
         <f>+Rounds!B7*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C5" s="13">
         <f>SUM(Rounds!C7:BB7)</f>
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="8">
         <f>+C5/(Rounds!$B$3*Rounds!B7)</f>
-        <v>1.5833333333333333</v>
+        <v>1.3571428571428572</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -645,15 +645,15 @@
       </c>
       <c r="B6" s="13">
         <f>+Rounds!B8*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C6" s="13">
         <f>SUM(Rounds!C8:BB8)</f>
-        <v>180.37</v>
+        <v>221.35</v>
       </c>
       <c r="D6" s="8">
         <f>+C6/(Rounds!$B$3*Rounds!B8)</f>
-        <v>1.5030833333333333</v>
+        <v>1.5810714285714285</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -662,7 +662,7 @@
       </c>
       <c r="B7" s="13">
         <f>+Rounds!B9*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C7" s="13">
         <f>SUM(Rounds!C9:BB9)</f>
@@ -670,7 +670,7 @@
       </c>
       <c r="D7" s="8">
         <f>+C7/(Rounds!$B$3*Rounds!B9)</f>
-        <v>1.31125</v>
+        <v>1.1239285714285714</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -679,7 +679,7 @@
       </c>
       <c r="B8" s="13">
         <f>+Rounds!B10*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C8" s="13">
         <f>SUM(Rounds!C10:BB10)</f>
@@ -687,7 +687,7 @@
       </c>
       <c r="D8" s="8">
         <f>+C8/(Rounds!$B$3*Rounds!B10)</f>
-        <v>1.2166666666666666</v>
+        <v>1.0428571428571429</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -696,15 +696,15 @@
       </c>
       <c r="B9" s="13">
         <f>+Rounds!B11*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C9" s="13">
         <f>SUM(Rounds!C11:BB11)</f>
-        <v>139</v>
+        <v>198</v>
       </c>
       <c r="D9" s="8">
         <f>+C9/(Rounds!$B$3*Rounds!B11)</f>
-        <v>1.1583333333333334</v>
+        <v>1.4142857142857144</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -713,15 +713,15 @@
       </c>
       <c r="B10" s="13">
         <f>+Rounds!B12*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C10" s="13">
         <f>SUM(Rounds!C12:BB12)</f>
-        <v>89.19</v>
+        <v>142.32</v>
       </c>
       <c r="D10" s="8">
         <f>+C10/(Rounds!$B$3*Rounds!B12)</f>
-        <v>0.74324999999999997</v>
+        <v>1.0165714285714285</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -730,7 +730,7 @@
       </c>
       <c r="B11" s="13">
         <f>+Rounds!B13*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C11" s="13">
         <f>SUM(Rounds!C13:BB13)</f>
@@ -738,7 +738,7 @@
       </c>
       <c r="D11" s="8">
         <f>+C11/(Rounds!$B$3*Rounds!B13)</f>
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -747,7 +747,7 @@
       </c>
       <c r="B12" s="13">
         <f>+Rounds!B14*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C12" s="13">
         <f>SUM(Rounds!C14:BB14)</f>
@@ -755,7 +755,7 @@
       </c>
       <c r="D12" s="8">
         <f>+C12/(Rounds!$B$3*Rounds!B14)</f>
-        <v>0.58333333333333337</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -764,7 +764,7 @@
       </c>
       <c r="B13" s="13">
         <f>+Rounds!B15*Rounds!$B$3</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C13" s="13">
         <f>SUM(Rounds!C15:BB15)</f>
@@ -772,7 +772,7 @@
       </c>
       <c r="D13" s="8">
         <f>+C13/(Rounds!$B$3*Rounds!B15)</f>
-        <v>0.2578333333333333</v>
+        <v>0.22099999999999997</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -787,15 +787,15 @@
       </c>
       <c r="B15" s="15">
         <f>SUM(B4:B13)</f>
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="C15" s="14">
         <f>SUM(C4:C13)</f>
-        <v>1282.5900000000001</v>
+        <v>1511.7</v>
       </c>
       <c r="D15" s="10">
         <f>+C15/(Rounds!$B$3*Rounds!B16)</f>
-        <v>1.0688250000000001</v>
+        <v>1.0797857142857143</v>
       </c>
     </row>
   </sheetData>
@@ -828,7 +828,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.2">
@@ -1068,7 +1068,9 @@
       <c r="H6" s="17">
         <v>64</v>
       </c>
-      <c r="I6" s="17"/>
+      <c r="I6" s="17">
+        <v>76</v>
+      </c>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
@@ -1200,7 +1202,9 @@
       <c r="H8" s="17">
         <v>65.67</v>
       </c>
-      <c r="I8" s="17"/>
+      <c r="I8" s="17">
+        <v>40.98</v>
+      </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
@@ -1397,7 +1401,9 @@
         <v>67.5</v>
       </c>
       <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
+      <c r="I11" s="17">
+        <v>59</v>
+      </c>
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
       <c r="L11" s="17"/>
@@ -1464,7 +1470,10 @@
         <v>20</v>
       </c>
       <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
+      <c r="I12" s="17">
+        <f>18.13+35</f>
+        <v>53.129999999999995</v>
+      </c>
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
@@ -1738,7 +1747,7 @@
       </c>
       <c r="I16" s="18">
         <f t="shared" ref="I16" si="5">SUM(I6:I15)</f>
-        <v>0</v>
+        <v>229.10999999999999</v>
       </c>
       <c r="J16" s="18">
         <f t="shared" ref="J16" si="6">SUM(J6:J15)</f>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="277" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FEE87DA-A963-4BC0-B949-C978FB7A1DA4}"/>
+  <xr:revisionPtr revIDLastSave="278" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{886C9369-6319-4AD5-BF32-2A6C33FE53EC}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
@@ -255,10 +255,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -683,11 +679,11 @@
       </c>
       <c r="C8" s="13">
         <f>SUM(Rounds!C10:BB10)</f>
-        <v>146</v>
+        <v>246</v>
       </c>
       <c r="D8" s="8">
         <f>+C8/(Rounds!$B$3*Rounds!B10)</f>
-        <v>1.0428571428571429</v>
+        <v>1.7571428571428571</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -791,11 +787,11 @@
       </c>
       <c r="C15" s="14">
         <f>SUM(C4:C13)</f>
-        <v>1511.7</v>
+        <v>1611.7</v>
       </c>
       <c r="D15" s="10">
         <f>+C15/(Rounds!$B$3*Rounds!B16)</f>
-        <v>1.0797857142857143</v>
+        <v>1.1512142857142857</v>
       </c>
     </row>
   </sheetData>
@@ -1334,7 +1330,9 @@
       </c>
       <c r="G10" s="17"/>
       <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
+      <c r="I10" s="17">
+        <v>100</v>
+      </c>
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
       <c r="L10" s="17"/>
@@ -1747,7 +1745,7 @@
       </c>
       <c r="I16" s="18">
         <f t="shared" ref="I16" si="5">SUM(I6:I15)</f>
-        <v>229.10999999999999</v>
+        <v>329.11</v>
       </c>
       <c r="J16" s="18">
         <f t="shared" ref="J16" si="6">SUM(J6:J15)</f>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="278" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{886C9369-6319-4AD5-BF32-2A6C33FE53EC}"/>
+  <xr:revisionPtr revIDLastSave="279" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C9672D6-08ED-4B27-8B5E-7307EE8DBB14}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
@@ -679,11 +679,11 @@
       </c>
       <c r="C8" s="13">
         <f>SUM(Rounds!C10:BB10)</f>
-        <v>246</v>
+        <v>146</v>
       </c>
       <c r="D8" s="8">
         <f>+C8/(Rounds!$B$3*Rounds!B10)</f>
-        <v>1.7571428571428571</v>
+        <v>1.0428571428571429</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -787,11 +787,11 @@
       </c>
       <c r="C15" s="14">
         <f>SUM(C4:C13)</f>
-        <v>1611.7</v>
+        <v>1511.7</v>
       </c>
       <c r="D15" s="10">
         <f>+C15/(Rounds!$B$3*Rounds!B16)</f>
-        <v>1.1512142857142857</v>
+        <v>1.0797857142857143</v>
       </c>
     </row>
   </sheetData>
@@ -1330,9 +1330,7 @@
       </c>
       <c r="G10" s="17"/>
       <c r="H10" s="17"/>
-      <c r="I10" s="17">
-        <v>100</v>
-      </c>
+      <c r="I10" s="17"/>
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
       <c r="L10" s="17"/>
@@ -1745,7 +1743,7 @@
       </c>
       <c r="I16" s="18">
         <f t="shared" ref="I16" si="5">SUM(I6:I15)</f>
-        <v>329.11</v>
+        <v>229.10999999999999</v>
       </c>
       <c r="J16" s="18">
         <f t="shared" ref="J16" si="6">SUM(J6:J15)</f>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="279" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C9672D6-08ED-4B27-8B5E-7307EE8DBB14}"/>
+  <xr:revisionPtr revIDLastSave="283" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81B4479D-AC22-4BFF-A74D-C20CF6B5D3C1}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="13">
         <f>+Rounds!B6*Rounds!$B$3</f>
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C4" s="13">
         <f>SUM(Rounds!C6:BB6)</f>
@@ -615,7 +615,7 @@
       </c>
       <c r="D4" s="8">
         <f>+C4/(Rounds!$B$3*Rounds!B6)</f>
-        <v>1.9410000000000001</v>
+        <v>1.698375</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -624,15 +624,15 @@
       </c>
       <c r="B5" s="13">
         <f>+Rounds!B7*Rounds!$B$3</f>
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C5" s="13">
         <f>SUM(Rounds!C7:BB7)</f>
-        <v>190</v>
+        <v>210.72</v>
       </c>
       <c r="D5" s="8">
         <f>+C5/(Rounds!$B$3*Rounds!B7)</f>
-        <v>1.3571428571428572</v>
+        <v>1.3169999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -641,7 +641,7 @@
       </c>
       <c r="B6" s="13">
         <f>+Rounds!B8*Rounds!$B$3</f>
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C6" s="13">
         <f>SUM(Rounds!C8:BB8)</f>
@@ -649,7 +649,7 @@
       </c>
       <c r="D6" s="8">
         <f>+C6/(Rounds!$B$3*Rounds!B8)</f>
-        <v>1.5810714285714285</v>
+        <v>1.3834374999999999</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -658,7 +658,7 @@
       </c>
       <c r="B7" s="13">
         <f>+Rounds!B9*Rounds!$B$3</f>
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C7" s="13">
         <f>SUM(Rounds!C9:BB9)</f>
@@ -666,7 +666,7 @@
       </c>
       <c r="D7" s="8">
         <f>+C7/(Rounds!$B$3*Rounds!B9)</f>
-        <v>1.1239285714285714</v>
+        <v>0.98343749999999996</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -675,7 +675,7 @@
       </c>
       <c r="B8" s="13">
         <f>+Rounds!B10*Rounds!$B$3</f>
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C8" s="13">
         <f>SUM(Rounds!C10:BB10)</f>
@@ -683,7 +683,7 @@
       </c>
       <c r="D8" s="8">
         <f>+C8/(Rounds!$B$3*Rounds!B10)</f>
-        <v>1.0428571428571429</v>
+        <v>0.91249999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -692,7 +692,7 @@
       </c>
       <c r="B9" s="13">
         <f>+Rounds!B11*Rounds!$B$3</f>
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C9" s="13">
         <f>SUM(Rounds!C11:BB11)</f>
@@ -700,7 +700,7 @@
       </c>
       <c r="D9" s="8">
         <f>+C9/(Rounds!$B$3*Rounds!B11)</f>
-        <v>1.4142857142857144</v>
+        <v>1.2375</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -709,7 +709,7 @@
       </c>
       <c r="B10" s="13">
         <f>+Rounds!B12*Rounds!$B$3</f>
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C10" s="13">
         <f>SUM(Rounds!C12:BB12)</f>
@@ -717,7 +717,7 @@
       </c>
       <c r="D10" s="8">
         <f>+C10/(Rounds!$B$3*Rounds!B12)</f>
-        <v>1.0165714285714285</v>
+        <v>0.88949999999999996</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -726,15 +726,15 @@
       </c>
       <c r="B11" s="13">
         <f>+Rounds!B13*Rounds!$B$3</f>
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C11" s="13">
         <f>SUM(Rounds!C13:BB13)</f>
-        <v>84</v>
+        <v>99.89</v>
       </c>
       <c r="D11" s="8">
         <f>+C11/(Rounds!$B$3*Rounds!B13)</f>
-        <v>0.6</v>
+        <v>0.62431250000000005</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -743,15 +743,15 @@
       </c>
       <c r="B12" s="13">
         <f>+Rounds!B14*Rounds!$B$3</f>
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C12" s="13">
         <f>SUM(Rounds!C14:BB14)</f>
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="D12" s="8">
         <f>+C12/(Rounds!$B$3*Rounds!B14)</f>
-        <v>0.5</v>
+        <v>0.66874999999999996</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" s="13">
         <f>+Rounds!B15*Rounds!$B$3</f>
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C13" s="13">
         <f>SUM(Rounds!C15:BB15)</f>
@@ -768,7 +768,7 @@
       </c>
       <c r="D13" s="8">
         <f>+C13/(Rounds!$B$3*Rounds!B15)</f>
-        <v>0.22099999999999997</v>
+        <v>0.19337499999999999</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -783,15 +783,15 @@
       </c>
       <c r="B15" s="15">
         <f>SUM(B4:B13)</f>
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="C15" s="14">
         <f>SUM(C4:C13)</f>
-        <v>1511.7</v>
+        <v>1585.3100000000002</v>
       </c>
       <c r="D15" s="10">
         <f>+C15/(Rounds!$B$3*Rounds!B16)</f>
-        <v>1.0797857142857143</v>
+        <v>0.99081875000000008</v>
       </c>
     </row>
   </sheetData>
@@ -824,7 +824,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.2">
@@ -1132,7 +1132,9 @@
         <v>150</v>
       </c>
       <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
+      <c r="J7" s="17">
+        <v>20.72</v>
+      </c>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
@@ -1535,7 +1537,9 @@
         <v>50</v>
       </c>
       <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
+      <c r="J13" s="17">
+        <v>15.89</v>
+      </c>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
@@ -1598,7 +1602,9 @@
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
+      <c r="J14" s="17">
+        <v>37</v>
+      </c>
       <c r="K14" s="17"/>
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
@@ -1747,7 +1753,7 @@
       </c>
       <c r="J16" s="18">
         <f t="shared" ref="J16" si="6">SUM(J6:J15)</f>
-        <v>0</v>
+        <v>73.61</v>
       </c>
       <c r="K16" s="18">
         <f t="shared" ref="K16" si="7">SUM(K6:K15)</f>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/Punters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="283" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81B4479D-AC22-4BFF-A74D-C20CF6B5D3C1}"/>
+  <xr:revisionPtr revIDLastSave="285" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F1888EA-2F7B-4388-9A50-259DEA22ACC9}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
+    <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -255,6 +255,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -607,7 +611,7 @@
       </c>
       <c r="B4" s="13">
         <f>+Rounds!B6*Rounds!$B$3</f>
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="C4" s="13">
         <f>SUM(Rounds!C6:BB6)</f>
@@ -615,7 +619,7 @@
       </c>
       <c r="D4" s="8">
         <f>+C4/(Rounds!$B$3*Rounds!B6)</f>
-        <v>1.698375</v>
+        <v>1.5096666666666667</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -624,7 +628,7 @@
       </c>
       <c r="B5" s="13">
         <f>+Rounds!B7*Rounds!$B$3</f>
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="C5" s="13">
         <f>SUM(Rounds!C7:BB7)</f>
@@ -632,7 +636,7 @@
       </c>
       <c r="D5" s="8">
         <f>+C5/(Rounds!$B$3*Rounds!B7)</f>
-        <v>1.3169999999999999</v>
+        <v>1.1706666666666667</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -641,7 +645,7 @@
       </c>
       <c r="B6" s="13">
         <f>+Rounds!B8*Rounds!$B$3</f>
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="C6" s="13">
         <f>SUM(Rounds!C8:BB8)</f>
@@ -649,7 +653,7 @@
       </c>
       <c r="D6" s="8">
         <f>+C6/(Rounds!$B$3*Rounds!B8)</f>
-        <v>1.3834374999999999</v>
+        <v>1.2297222222222222</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -658,7 +662,7 @@
       </c>
       <c r="B7" s="13">
         <f>+Rounds!B9*Rounds!$B$3</f>
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="C7" s="13">
         <f>SUM(Rounds!C9:BB9)</f>
@@ -666,7 +670,7 @@
       </c>
       <c r="D7" s="8">
         <f>+C7/(Rounds!$B$3*Rounds!B9)</f>
-        <v>0.98343749999999996</v>
+        <v>0.87416666666666665</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -675,7 +679,7 @@
       </c>
       <c r="B8" s="13">
         <f>+Rounds!B10*Rounds!$B$3</f>
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="C8" s="13">
         <f>SUM(Rounds!C10:BB10)</f>
@@ -683,7 +687,7 @@
       </c>
       <c r="D8" s="8">
         <f>+C8/(Rounds!$B$3*Rounds!B10)</f>
-        <v>0.91249999999999998</v>
+        <v>0.81111111111111112</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -692,7 +696,7 @@
       </c>
       <c r="B9" s="13">
         <f>+Rounds!B11*Rounds!$B$3</f>
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="C9" s="13">
         <f>SUM(Rounds!C11:BB11)</f>
@@ -700,7 +704,7 @@
       </c>
       <c r="D9" s="8">
         <f>+C9/(Rounds!$B$3*Rounds!B11)</f>
-        <v>1.2375</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -709,15 +713,15 @@
       </c>
       <c r="B10" s="13">
         <f>+Rounds!B12*Rounds!$B$3</f>
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="C10" s="13">
         <f>SUM(Rounds!C12:BB12)</f>
-        <v>142.32</v>
+        <v>192.32</v>
       </c>
       <c r="D10" s="8">
         <f>+C10/(Rounds!$B$3*Rounds!B12)</f>
-        <v>0.88949999999999996</v>
+        <v>1.0684444444444443</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -726,7 +730,7 @@
       </c>
       <c r="B11" s="13">
         <f>+Rounds!B13*Rounds!$B$3</f>
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="C11" s="13">
         <f>SUM(Rounds!C13:BB13)</f>
@@ -734,7 +738,7 @@
       </c>
       <c r="D11" s="8">
         <f>+C11/(Rounds!$B$3*Rounds!B13)</f>
-        <v>0.62431250000000005</v>
+        <v>0.55494444444444446</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -743,7 +747,7 @@
       </c>
       <c r="B12" s="13">
         <f>+Rounds!B14*Rounds!$B$3</f>
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="C12" s="13">
         <f>SUM(Rounds!C14:BB14)</f>
@@ -751,7 +755,7 @@
       </c>
       <c r="D12" s="8">
         <f>+C12/(Rounds!$B$3*Rounds!B14)</f>
-        <v>0.66874999999999996</v>
+        <v>0.59444444444444444</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -760,7 +764,7 @@
       </c>
       <c r="B13" s="13">
         <f>+Rounds!B15*Rounds!$B$3</f>
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="C13" s="13">
         <f>SUM(Rounds!C15:BB15)</f>
@@ -768,7 +772,7 @@
       </c>
       <c r="D13" s="8">
         <f>+C13/(Rounds!$B$3*Rounds!B15)</f>
-        <v>0.19337499999999999</v>
+        <v>0.17188888888888887</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -783,15 +787,15 @@
       </c>
       <c r="B15" s="15">
         <f>SUM(B4:B13)</f>
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="C15" s="14">
         <f>SUM(C4:C13)</f>
-        <v>1585.3100000000002</v>
+        <v>1635.3100000000002</v>
       </c>
       <c r="D15" s="10">
         <f>+C15/(Rounds!$B$3*Rounds!B16)</f>
-        <v>0.99081875000000008</v>
+        <v>0.90850555555555568</v>
       </c>
     </row>
   </sheetData>
@@ -824,7 +828,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.2">
@@ -1473,7 +1477,9 @@
         <v>53.129999999999995</v>
       </c>
       <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
+      <c r="K12" s="17">
+        <v>50</v>
+      </c>
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
       <c r="N12" s="17"/>
@@ -1757,7 +1763,7 @@
       </c>
       <c r="K16" s="18">
         <f t="shared" ref="K16" si="7">SUM(K6:K15)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L16" s="18">
         <f t="shared" ref="L16" si="8">SUM(L6:L15)</f>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/Punters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="285" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F1888EA-2F7B-4388-9A50-259DEA22ACC9}"/>
+  <xr:revisionPtr revIDLastSave="289" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38A0307B-C7FD-467D-872D-602F6E973B76}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
@@ -255,10 +255,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -611,7 +607,7 @@
       </c>
       <c r="B4" s="13">
         <f>+Rounds!B6*Rounds!$B$3</f>
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C4" s="13">
         <f>SUM(Rounds!C6:BB6)</f>
@@ -619,7 +615,7 @@
       </c>
       <c r="D4" s="8">
         <f>+C4/(Rounds!$B$3*Rounds!B6)</f>
-        <v>1.5096666666666667</v>
+        <v>1.3587</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -628,7 +624,7 @@
       </c>
       <c r="B5" s="13">
         <f>+Rounds!B7*Rounds!$B$3</f>
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C5" s="13">
         <f>SUM(Rounds!C7:BB7)</f>
@@ -636,7 +632,7 @@
       </c>
       <c r="D5" s="8">
         <f>+C5/(Rounds!$B$3*Rounds!B7)</f>
-        <v>1.1706666666666667</v>
+        <v>1.0536000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -645,7 +641,7 @@
       </c>
       <c r="B6" s="13">
         <f>+Rounds!B8*Rounds!$B$3</f>
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C6" s="13">
         <f>SUM(Rounds!C8:BB8)</f>
@@ -653,7 +649,7 @@
       </c>
       <c r="D6" s="8">
         <f>+C6/(Rounds!$B$3*Rounds!B8)</f>
-        <v>1.2297222222222222</v>
+        <v>1.1067499999999999</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -662,15 +658,15 @@
       </c>
       <c r="B7" s="13">
         <f>+Rounds!B9*Rounds!$B$3</f>
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C7" s="13">
         <f>SUM(Rounds!C9:BB9)</f>
-        <v>157.35</v>
+        <v>307.89</v>
       </c>
       <c r="D7" s="8">
         <f>+C7/(Rounds!$B$3*Rounds!B9)</f>
-        <v>0.87416666666666665</v>
+        <v>1.53945</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -679,7 +675,7 @@
       </c>
       <c r="B8" s="13">
         <f>+Rounds!B10*Rounds!$B$3</f>
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C8" s="13">
         <f>SUM(Rounds!C10:BB10)</f>
@@ -687,7 +683,7 @@
       </c>
       <c r="D8" s="8">
         <f>+C8/(Rounds!$B$3*Rounds!B10)</f>
-        <v>0.81111111111111112</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -696,15 +692,15 @@
       </c>
       <c r="B9" s="13">
         <f>+Rounds!B11*Rounds!$B$3</f>
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C9" s="13">
         <f>SUM(Rounds!C11:BB11)</f>
-        <v>198</v>
+        <v>234.25</v>
       </c>
       <c r="D9" s="8">
         <f>+C9/(Rounds!$B$3*Rounds!B11)</f>
-        <v>1.1000000000000001</v>
+        <v>1.1712499999999999</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -713,15 +709,15 @@
       </c>
       <c r="B10" s="13">
         <f>+Rounds!B12*Rounds!$B$3</f>
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C10" s="13">
         <f>SUM(Rounds!C12:BB12)</f>
-        <v>192.32</v>
+        <v>241.32</v>
       </c>
       <c r="D10" s="8">
         <f>+C10/(Rounds!$B$3*Rounds!B12)</f>
-        <v>1.0684444444444443</v>
+        <v>1.2065999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -730,7 +726,7 @@
       </c>
       <c r="B11" s="13">
         <f>+Rounds!B13*Rounds!$B$3</f>
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C11" s="13">
         <f>SUM(Rounds!C13:BB13)</f>
@@ -738,7 +734,7 @@
       </c>
       <c r="D11" s="8">
         <f>+C11/(Rounds!$B$3*Rounds!B13)</f>
-        <v>0.55494444444444446</v>
+        <v>0.49945000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -747,7 +743,7 @@
       </c>
       <c r="B12" s="13">
         <f>+Rounds!B14*Rounds!$B$3</f>
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C12" s="13">
         <f>SUM(Rounds!C14:BB14)</f>
@@ -755,7 +751,7 @@
       </c>
       <c r="D12" s="8">
         <f>+C12/(Rounds!$B$3*Rounds!B14)</f>
-        <v>0.59444444444444444</v>
+        <v>0.53500000000000003</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -764,7 +760,7 @@
       </c>
       <c r="B13" s="13">
         <f>+Rounds!B15*Rounds!$B$3</f>
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C13" s="13">
         <f>SUM(Rounds!C15:BB15)</f>
@@ -772,7 +768,7 @@
       </c>
       <c r="D13" s="8">
         <f>+C13/(Rounds!$B$3*Rounds!B15)</f>
-        <v>0.17188888888888887</v>
+        <v>0.15469999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -787,15 +783,15 @@
       </c>
       <c r="B15" s="15">
         <f>SUM(B4:B13)</f>
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="C15" s="14">
         <f>SUM(C4:C13)</f>
-        <v>1635.3100000000002</v>
+        <v>1871.1000000000001</v>
       </c>
       <c r="D15" s="10">
         <f>+C15/(Rounds!$B$3*Rounds!B16)</f>
-        <v>0.90850555555555568</v>
+        <v>0.9355500000000001</v>
       </c>
     </row>
   </sheetData>
@@ -828,7 +824,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.2">
@@ -1274,7 +1270,9 @@
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
+      <c r="L9" s="17">
+        <v>150.54</v>
+      </c>
       <c r="M9" s="17"/>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
@@ -1408,7 +1406,9 @@
       </c>
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
+      <c r="L11" s="17">
+        <v>36.25</v>
+      </c>
       <c r="M11" s="17"/>
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
@@ -1480,7 +1480,9 @@
       <c r="K12" s="17">
         <v>50</v>
       </c>
-      <c r="L12" s="17"/>
+      <c r="L12" s="17">
+        <v>49</v>
+      </c>
       <c r="M12" s="17"/>
       <c r="N12" s="17"/>
       <c r="O12" s="17"/>
@@ -1767,7 +1769,7 @@
       </c>
       <c r="L16" s="18">
         <f t="shared" ref="L16" si="8">SUM(L6:L15)</f>
-        <v>0</v>
+        <v>235.79</v>
       </c>
       <c r="M16" s="18">
         <f t="shared" ref="M16" si="9">SUM(M6:M15)</f>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/Punters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="289" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38A0307B-C7FD-467D-872D-602F6E973B76}"/>
+  <xr:revisionPtr revIDLastSave="292" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{364DC0FA-41D7-4116-B084-5EF864310A38}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
@@ -255,6 +255,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -607,7 +611,7 @@
       </c>
       <c r="B4" s="13">
         <f>+Rounds!B6*Rounds!$B$3</f>
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="C4" s="13">
         <f>SUM(Rounds!C6:BB6)</f>
@@ -615,7 +619,7 @@
       </c>
       <c r="D4" s="8">
         <f>+C4/(Rounds!$B$3*Rounds!B6)</f>
-        <v>1.3587</v>
+        <v>1.2351818181818182</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -624,7 +628,7 @@
       </c>
       <c r="B5" s="13">
         <f>+Rounds!B7*Rounds!$B$3</f>
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="C5" s="13">
         <f>SUM(Rounds!C7:BB7)</f>
@@ -632,7 +636,7 @@
       </c>
       <c r="D5" s="8">
         <f>+C5/(Rounds!$B$3*Rounds!B7)</f>
-        <v>1.0536000000000001</v>
+        <v>0.95781818181818179</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -641,7 +645,7 @@
       </c>
       <c r="B6" s="13">
         <f>+Rounds!B8*Rounds!$B$3</f>
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="C6" s="13">
         <f>SUM(Rounds!C8:BB8)</f>
@@ -649,7 +653,7 @@
       </c>
       <c r="D6" s="8">
         <f>+C6/(Rounds!$B$3*Rounds!B8)</f>
-        <v>1.1067499999999999</v>
+        <v>1.0061363636363636</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -658,7 +662,7 @@
       </c>
       <c r="B7" s="13">
         <f>+Rounds!B9*Rounds!$B$3</f>
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="C7" s="13">
         <f>SUM(Rounds!C9:BB9)</f>
@@ -666,7 +670,7 @@
       </c>
       <c r="D7" s="8">
         <f>+C7/(Rounds!$B$3*Rounds!B9)</f>
-        <v>1.53945</v>
+        <v>1.3995</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -675,7 +679,7 @@
       </c>
       <c r="B8" s="13">
         <f>+Rounds!B10*Rounds!$B$3</f>
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="C8" s="13">
         <f>SUM(Rounds!C10:BB10)</f>
@@ -683,7 +687,7 @@
       </c>
       <c r="D8" s="8">
         <f>+C8/(Rounds!$B$3*Rounds!B10)</f>
-        <v>0.73</v>
+        <v>0.66363636363636369</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -692,15 +696,15 @@
       </c>
       <c r="B9" s="13">
         <f>+Rounds!B11*Rounds!$B$3</f>
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="C9" s="13">
         <f>SUM(Rounds!C11:BB11)</f>
-        <v>234.25</v>
+        <v>251.75</v>
       </c>
       <c r="D9" s="8">
         <f>+C9/(Rounds!$B$3*Rounds!B11)</f>
-        <v>1.1712499999999999</v>
+        <v>1.1443181818181818</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -709,15 +713,15 @@
       </c>
       <c r="B10" s="13">
         <f>+Rounds!B12*Rounds!$B$3</f>
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="C10" s="13">
         <f>SUM(Rounds!C12:BB12)</f>
-        <v>241.32</v>
+        <v>278.18</v>
       </c>
       <c r="D10" s="8">
         <f>+C10/(Rounds!$B$3*Rounds!B12)</f>
-        <v>1.2065999999999999</v>
+        <v>1.2644545454545455</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -726,7 +730,7 @@
       </c>
       <c r="B11" s="13">
         <f>+Rounds!B13*Rounds!$B$3</f>
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="C11" s="13">
         <f>SUM(Rounds!C13:BB13)</f>
@@ -734,7 +738,7 @@
       </c>
       <c r="D11" s="8">
         <f>+C11/(Rounds!$B$3*Rounds!B13)</f>
-        <v>0.49945000000000001</v>
+        <v>0.45404545454545453</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -743,7 +747,7 @@
       </c>
       <c r="B12" s="13">
         <f>+Rounds!B14*Rounds!$B$3</f>
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="C12" s="13">
         <f>SUM(Rounds!C14:BB14)</f>
@@ -751,7 +755,7 @@
       </c>
       <c r="D12" s="8">
         <f>+C12/(Rounds!$B$3*Rounds!B14)</f>
-        <v>0.53500000000000003</v>
+        <v>0.48636363636363639</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -760,7 +764,7 @@
       </c>
       <c r="B13" s="13">
         <f>+Rounds!B15*Rounds!$B$3</f>
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="C13" s="13">
         <f>SUM(Rounds!C15:BB15)</f>
@@ -768,7 +772,7 @@
       </c>
       <c r="D13" s="8">
         <f>+C13/(Rounds!$B$3*Rounds!B15)</f>
-        <v>0.15469999999999998</v>
+        <v>0.14063636363636361</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -783,15 +787,15 @@
       </c>
       <c r="B15" s="15">
         <f>SUM(B4:B13)</f>
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="C15" s="14">
         <f>SUM(C4:C13)</f>
-        <v>1871.1000000000001</v>
+        <v>1925.4600000000003</v>
       </c>
       <c r="D15" s="10">
         <f>+C15/(Rounds!$B$3*Rounds!B16)</f>
-        <v>0.9355500000000001</v>
+        <v>0.87520909090909105</v>
       </c>
     </row>
   </sheetData>
@@ -824,7 +828,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.2">
@@ -1409,7 +1413,9 @@
       <c r="L11" s="17">
         <v>36.25</v>
       </c>
-      <c r="M11" s="17"/>
+      <c r="M11" s="17">
+        <v>17.5</v>
+      </c>
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
       <c r="P11" s="17"/>
@@ -1483,7 +1489,9 @@
       <c r="L12" s="17">
         <v>49</v>
       </c>
-      <c r="M12" s="17"/>
+      <c r="M12" s="17">
+        <v>36.86</v>
+      </c>
       <c r="N12" s="17"/>
       <c r="O12" s="17"/>
       <c r="P12" s="17"/>
@@ -1773,7 +1781,7 @@
       </c>
       <c r="M16" s="18">
         <f t="shared" ref="M16" si="9">SUM(M6:M15)</f>
-        <v>0</v>
+        <v>54.36</v>
       </c>
       <c r="N16" s="18">
         <f t="shared" ref="N16" si="10">SUM(N6:N15)</f>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/Punters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="292" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{364DC0FA-41D7-4116-B084-5EF864310A38}"/>
+  <xr:revisionPtr revIDLastSave="295" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2913B74-2B2F-46C0-A45C-88B75E510C2C}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
@@ -255,10 +255,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -611,7 +607,7 @@
       </c>
       <c r="B4" s="13">
         <f>+Rounds!B6*Rounds!$B$3</f>
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C4" s="13">
         <f>SUM(Rounds!C6:BB6)</f>
@@ -619,7 +615,7 @@
       </c>
       <c r="D4" s="8">
         <f>+C4/(Rounds!$B$3*Rounds!B6)</f>
-        <v>1.2351818181818182</v>
+        <v>1.13225</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -628,15 +624,15 @@
       </c>
       <c r="B5" s="13">
         <f>+Rounds!B7*Rounds!$B$3</f>
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C5" s="13">
         <f>SUM(Rounds!C7:BB7)</f>
-        <v>210.72</v>
+        <v>278.43</v>
       </c>
       <c r="D5" s="8">
         <f>+C5/(Rounds!$B$3*Rounds!B7)</f>
-        <v>0.95781818181818179</v>
+        <v>1.1601250000000001</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -645,7 +641,7 @@
       </c>
       <c r="B6" s="13">
         <f>+Rounds!B8*Rounds!$B$3</f>
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C6" s="13">
         <f>SUM(Rounds!C8:BB8)</f>
@@ -653,7 +649,7 @@
       </c>
       <c r="D6" s="8">
         <f>+C6/(Rounds!$B$3*Rounds!B8)</f>
-        <v>1.0061363636363636</v>
+        <v>0.92229166666666662</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -662,7 +658,7 @@
       </c>
       <c r="B7" s="13">
         <f>+Rounds!B9*Rounds!$B$3</f>
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C7" s="13">
         <f>SUM(Rounds!C9:BB9)</f>
@@ -670,7 +666,7 @@
       </c>
       <c r="D7" s="8">
         <f>+C7/(Rounds!$B$3*Rounds!B9)</f>
-        <v>1.3995</v>
+        <v>1.282875</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -679,7 +675,7 @@
       </c>
       <c r="B8" s="13">
         <f>+Rounds!B10*Rounds!$B$3</f>
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C8" s="13">
         <f>SUM(Rounds!C10:BB10)</f>
@@ -687,7 +683,7 @@
       </c>
       <c r="D8" s="8">
         <f>+C8/(Rounds!$B$3*Rounds!B10)</f>
-        <v>0.66363636363636369</v>
+        <v>0.60833333333333328</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -696,7 +692,7 @@
       </c>
       <c r="B9" s="13">
         <f>+Rounds!B11*Rounds!$B$3</f>
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C9" s="13">
         <f>SUM(Rounds!C11:BB11)</f>
@@ -704,7 +700,7 @@
       </c>
       <c r="D9" s="8">
         <f>+C9/(Rounds!$B$3*Rounds!B11)</f>
-        <v>1.1443181818181818</v>
+        <v>1.0489583333333334</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -713,7 +709,7 @@
       </c>
       <c r="B10" s="13">
         <f>+Rounds!B12*Rounds!$B$3</f>
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C10" s="13">
         <f>SUM(Rounds!C12:BB12)</f>
@@ -721,7 +717,7 @@
       </c>
       <c r="D10" s="8">
         <f>+C10/(Rounds!$B$3*Rounds!B12)</f>
-        <v>1.2644545454545455</v>
+        <v>1.1590833333333335</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -730,7 +726,7 @@
       </c>
       <c r="B11" s="13">
         <f>+Rounds!B13*Rounds!$B$3</f>
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C11" s="13">
         <f>SUM(Rounds!C13:BB13)</f>
@@ -738,7 +734,7 @@
       </c>
       <c r="D11" s="8">
         <f>+C11/(Rounds!$B$3*Rounds!B13)</f>
-        <v>0.45404545454545453</v>
+        <v>0.41620833333333335</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -747,15 +743,15 @@
       </c>
       <c r="B12" s="13">
         <f>+Rounds!B14*Rounds!$B$3</f>
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C12" s="13">
         <f>SUM(Rounds!C14:BB14)</f>
-        <v>107</v>
+        <v>130.5</v>
       </c>
       <c r="D12" s="8">
         <f>+C12/(Rounds!$B$3*Rounds!B14)</f>
-        <v>0.48636363636363639</v>
+        <v>0.54374999999999996</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -764,7 +760,7 @@
       </c>
       <c r="B13" s="13">
         <f>+Rounds!B15*Rounds!$B$3</f>
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C13" s="13">
         <f>SUM(Rounds!C15:BB15)</f>
@@ -772,7 +768,7 @@
       </c>
       <c r="D13" s="8">
         <f>+C13/(Rounds!$B$3*Rounds!B15)</f>
-        <v>0.14063636363636361</v>
+        <v>0.12891666666666665</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -787,15 +783,15 @@
       </c>
       <c r="B15" s="15">
         <f>SUM(B4:B13)</f>
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="C15" s="14">
         <f>SUM(C4:C13)</f>
-        <v>1925.4600000000003</v>
+        <v>2016.6700000000003</v>
       </c>
       <c r="D15" s="10">
         <f>+C15/(Rounds!$B$3*Rounds!B16)</f>
-        <v>0.87520909090909105</v>
+        <v>0.8402791666666668</v>
       </c>
     </row>
   </sheetData>
@@ -828,7 +824,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.2">
@@ -1142,7 +1138,9 @@
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
+      <c r="N7" s="17">
+        <v>67.709999999999994</v>
+      </c>
       <c r="O7" s="17"/>
       <c r="P7" s="17"/>
       <c r="Q7" s="17"/>
@@ -1624,7 +1622,9 @@
       <c r="K14" s="17"/>
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
+      <c r="N14" s="17">
+        <v>23.5</v>
+      </c>
       <c r="O14" s="17"/>
       <c r="P14" s="17"/>
       <c r="Q14" s="17"/>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="N16" s="18">
         <f t="shared" ref="N16" si="10">SUM(N6:N15)</f>
-        <v>0</v>
+        <v>91.21</v>
       </c>
       <c r="O16" s="18">
         <f t="shared" ref="O16" si="11">SUM(O6:O15)</f>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/Punters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="295" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2913B74-2B2F-46C0-A45C-88B75E510C2C}"/>
+  <xr:revisionPtr revIDLastSave="300" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F9F7281-DB77-43F5-9097-B5CD9F603AB7}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
@@ -255,6 +255,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -607,15 +611,15 @@
       </c>
       <c r="B4" s="13">
         <f>+Rounds!B6*Rounds!$B$3</f>
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C4" s="13">
         <f>SUM(Rounds!C6:BB6)</f>
-        <v>271.74</v>
+        <v>339.74</v>
       </c>
       <c r="D4" s="8">
         <f>+C4/(Rounds!$B$3*Rounds!B6)</f>
-        <v>1.13225</v>
+        <v>1.3066923076923078</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -624,7 +628,7 @@
       </c>
       <c r="B5" s="13">
         <f>+Rounds!B7*Rounds!$B$3</f>
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C5" s="13">
         <f>SUM(Rounds!C7:BB7)</f>
@@ -632,7 +636,7 @@
       </c>
       <c r="D5" s="8">
         <f>+C5/(Rounds!$B$3*Rounds!B7)</f>
-        <v>1.1601250000000001</v>
+        <v>1.0708846153846154</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -641,7 +645,7 @@
       </c>
       <c r="B6" s="13">
         <f>+Rounds!B8*Rounds!$B$3</f>
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C6" s="13">
         <f>SUM(Rounds!C8:BB8)</f>
@@ -649,7 +653,7 @@
       </c>
       <c r="D6" s="8">
         <f>+C6/(Rounds!$B$3*Rounds!B8)</f>
-        <v>0.92229166666666662</v>
+        <v>0.85134615384615386</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -658,7 +662,7 @@
       </c>
       <c r="B7" s="13">
         <f>+Rounds!B9*Rounds!$B$3</f>
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C7" s="13">
         <f>SUM(Rounds!C9:BB9)</f>
@@ -666,7 +670,7 @@
       </c>
       <c r="D7" s="8">
         <f>+C7/(Rounds!$B$3*Rounds!B9)</f>
-        <v>1.282875</v>
+        <v>1.1841923076923075</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -675,15 +679,15 @@
       </c>
       <c r="B8" s="13">
         <f>+Rounds!B10*Rounds!$B$3</f>
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C8" s="13">
         <f>SUM(Rounds!C10:BB10)</f>
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="D8" s="8">
         <f>+C8/(Rounds!$B$3*Rounds!B10)</f>
-        <v>0.60833333333333328</v>
+        <v>0.63846153846153841</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -692,7 +696,7 @@
       </c>
       <c r="B9" s="13">
         <f>+Rounds!B11*Rounds!$B$3</f>
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C9" s="13">
         <f>SUM(Rounds!C11:BB11)</f>
@@ -700,7 +704,7 @@
       </c>
       <c r="D9" s="8">
         <f>+C9/(Rounds!$B$3*Rounds!B11)</f>
-        <v>1.0489583333333334</v>
+        <v>0.96826923076923077</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -709,7 +713,7 @@
       </c>
       <c r="B10" s="13">
         <f>+Rounds!B12*Rounds!$B$3</f>
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C10" s="13">
         <f>SUM(Rounds!C12:BB12)</f>
@@ -717,7 +721,7 @@
       </c>
       <c r="D10" s="8">
         <f>+C10/(Rounds!$B$3*Rounds!B12)</f>
-        <v>1.1590833333333335</v>
+        <v>1.069923076923077</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -726,15 +730,15 @@
       </c>
       <c r="B11" s="13">
         <f>+Rounds!B13*Rounds!$B$3</f>
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C11" s="13">
         <f>SUM(Rounds!C13:BB13)</f>
-        <v>99.89</v>
+        <v>219.89</v>
       </c>
       <c r="D11" s="8">
         <f>+C11/(Rounds!$B$3*Rounds!B13)</f>
-        <v>0.41620833333333335</v>
+        <v>0.84573076923076917</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -743,7 +747,7 @@
       </c>
       <c r="B12" s="13">
         <f>+Rounds!B14*Rounds!$B$3</f>
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C12" s="13">
         <f>SUM(Rounds!C14:BB14)</f>
@@ -751,7 +755,7 @@
       </c>
       <c r="D12" s="8">
         <f>+C12/(Rounds!$B$3*Rounds!B14)</f>
-        <v>0.54374999999999996</v>
+        <v>0.50192307692307692</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -760,15 +764,15 @@
       </c>
       <c r="B13" s="13">
         <f>+Rounds!B15*Rounds!$B$3</f>
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C13" s="13">
         <f>SUM(Rounds!C15:BB15)</f>
-        <v>30.939999999999998</v>
+        <v>210.94</v>
       </c>
       <c r="D13" s="8">
         <f>+C13/(Rounds!$B$3*Rounds!B15)</f>
-        <v>0.12891666666666665</v>
+        <v>0.81130769230769229</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -783,15 +787,15 @@
       </c>
       <c r="B15" s="15">
         <f>SUM(B4:B13)</f>
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="C15" s="14">
         <f>SUM(C4:C13)</f>
-        <v>2016.6700000000003</v>
+        <v>2404.67</v>
       </c>
       <c r="D15" s="10">
         <f>+C15/(Rounds!$B$3*Rounds!B16)</f>
-        <v>0.8402791666666668</v>
+        <v>0.92487307692307696</v>
       </c>
     </row>
   </sheetData>
@@ -824,7 +828,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.2">
@@ -1072,7 +1076,9 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
+      <c r="O6" s="17">
+        <v>68</v>
+      </c>
       <c r="P6" s="17"/>
       <c r="Q6" s="17"/>
       <c r="R6" s="17"/>
@@ -1342,7 +1348,9 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
+      <c r="O10" s="17">
+        <v>20</v>
+      </c>
       <c r="P10" s="17"/>
       <c r="Q10" s="17"/>
       <c r="R10" s="17"/>
@@ -1558,7 +1566,9 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
+      <c r="O13" s="17">
+        <v>120</v>
+      </c>
       <c r="P13" s="17"/>
       <c r="Q13" s="17"/>
       <c r="R13" s="17"/>
@@ -1690,7 +1700,9 @@
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
+      <c r="O15" s="17">
+        <v>180</v>
+      </c>
       <c r="P15" s="17"/>
       <c r="Q15" s="17"/>
       <c r="R15" s="17"/>
@@ -1789,7 +1801,7 @@
       </c>
       <c r="O16" s="18">
         <f t="shared" ref="O16" si="11">SUM(O6:O15)</f>
-        <v>0</v>
+        <v>388</v>
       </c>
       <c r="P16" s="18">
         <f t="shared" ref="P16" si="12">SUM(P6:P15)</f>
